--- a/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
+++ b/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
@@ -7370,148 +7370,148 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="n">
+      <c r="A88" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>要確認（結果が未確定）</t>
         </is>
       </c>
-      <c r="D88" s="9" t="inlineStr">
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>K14 横断的な観点の総括確認</t>
         </is>
       </c>
-      <c r="E88" s="9" t="inlineStr">
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>E-31</t>
         </is>
       </c>
-      <c r="F88" s="9" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <t>重点項目(全量一覧No別)</t>
         </is>
       </c>
-      <c r="G88" s="9" t="n">
+      <c r="G88" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="H88" s="9" t="inlineStr">
+      <c r="H88" s="6" t="inlineStr">
         <is>
           <t>全量一覧 No.33・34 / テスト・アンケート</t>
         </is>
       </c>
-      <c r="I88" s="9" t="inlineStr">
+      <c r="I88" s="6" t="inlineStr">
         <is>
           <t>設問・選択肢・備考・解説</t>
         </is>
       </c>
-      <c r="J88" s="9" t="inlineStr">
+      <c r="J88" s="6" t="inlineStr">
         <is>
           <t>タグを許可する項目</t>
         </is>
       </c>
-      <c r="K88" s="9" t="inlineStr">
+      <c r="K88" s="6" t="inlineStr">
         <is>
           <t>/exam/・/exam2/・/ethic_treaning/ の全画面(index・confirm・result・answer_check・resubmit…)、【CMS】/cms_exam_problem/・/cms_exam2_problem/(確認・Ajax)</t>
         </is>
       </c>
-      <c r="L88" s="9" t="inlineStr">
+      <c r="L88" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M88" s="9" t="inlineStr">
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N88" s="6" t="inlineStr">
+        <is>
+          <t>タグ許可ポリシー全体の横断確認。個別画面(exam/exam2のpurify_ethic_html適用等)は確認済みだが、総括としての確認はまだ</t>
+        </is>
+      </c>
+      <c r="O88" s="6" t="n"/>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>個別画面のテスト結果をもとに、観点ごとに総括して判定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>要確認（結果が未確定）</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>K14 横断的な観点の総括確認</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>E-34</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>重点項目(全量一覧No別)</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>全量一覧 No.37 / 全入力画面</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>入力欄の再表示(set_value)</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>入力値の往復</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>/(全入力画面)</t>
+        </is>
+      </c>
+      <c r="L89" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="N88" s="9" t="inlineStr">
-        <is>
-          <t>タグ許可ポリシー全体の横断確認。個別画面(exam/exam2のpurify_ethic_html適用等)は確認済みだが、総括としての確認はまだ</t>
-        </is>
-      </c>
-      <c r="O88" s="9" t="n"/>
-      <c r="P88" s="9" t="inlineStr">
-        <is>
-          <t>個別画面のテスト結果をもとに、観点ごとに総括して判定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="9" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>要確認（結果が未確定）</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>K14 横断的な観点の総括確認</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>E-34</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>重点項目(全量一覧No別)</t>
-        </is>
-      </c>
-      <c r="G89" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="H89" s="9" t="inlineStr">
-        <is>
-          <t>全量一覧 No.37 / 全入力画面</t>
-        </is>
-      </c>
-      <c r="I89" s="9" t="inlineStr">
-        <is>
-          <t>入力欄の再表示(set_value)</t>
-        </is>
-      </c>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>入力値の往復</t>
-        </is>
-      </c>
-      <c r="K89" s="9" t="inlineStr">
-        <is>
-          <t>/(全入力画面)</t>
-        </is>
-      </c>
-      <c r="L89" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M89" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N89" s="9" t="inlineStr">
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N89" s="6" t="inlineStr">
         <is>
           <t>横断的な観点(全入力画面の入力値往復・PC/SP差分)の総括確認はまだ。個別画面の確認は既存のS1〜S12テストで広くカバー済み</t>
         </is>
       </c>
-      <c r="O89" s="9" t="n"/>
-      <c r="P89" s="9" t="inlineStr">
+      <c r="O89" s="6" t="n"/>
+      <c r="P89" s="6" t="inlineStr">
         <is>
           <t>個別画面のテスト結果をもとに、観点ごとに総括して判定する。</t>
         </is>

--- a/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
+++ b/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
@@ -6403,370 +6403,370 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="9" t="n">
+      <c r="A75" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>要確認（結果が未確定）</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>K8 受講者登録の不具合の修正後の再テスト</t>
         </is>
       </c>
-      <c r="E75" s="9" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>B-0015</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>管理_商品管理</t>
         </is>
       </c>
-      <c r="G75" s="9" t="n">
+      <c r="G75" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="H75" s="9" t="inlineStr">
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>売上(注文)(amount_order)</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>詳細(info)</t>
         </is>
       </c>
-      <c r="J75" s="9" t="inlineStr">
+      <c r="J75" s="6" t="inlineStr">
         <is>
           <t>atena(atena)</t>
         </is>
       </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K75" s="6" t="inlineStr">
         <is>
           <t>/alfproduct/amount_order/info.php</t>
         </is>
       </c>
-      <c r="L75" s="9" t="inlineStr">
+      <c r="L75" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M75" s="9" t="inlineStr">
+      <c r="M75" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N75" s="6" t="inlineStr">
+        <is>
+          <t>テストハーネスの技術的制約(ページ遷移中のタイミング issue)、または[B-13]/[B-22]の修正により再テストで解消する可能性が高い</t>
+        </is>
+      </c>
+      <c r="O75" s="6" t="n"/>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>stg2 への反映を確認してから、run-xss-data-linked.js --accept-writes で再実行する（DBダンプを取得してから）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>要確認（結果が未確定）</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>K8 受講者登録の不具合の修正後の再テスト</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>B-0046</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>管理_商品管理</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>売上(会員)(amount_user)</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>詳細(info)</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>hidden項目(まとめ)</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>/alfproduct/amount_user/info.php</t>
+        </is>
+      </c>
+      <c r="L76" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="N75" s="9" t="inlineStr">
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N76" s="6" t="inlineStr">
         <is>
           <t>テストハーネスの技術的制約(ページ遷移中のタイミング issue)、または[B-13]/[B-22]の修正により再テストで解消する可能性が高い</t>
         </is>
       </c>
-      <c r="O75" s="9" t="n"/>
-      <c r="P75" s="9" t="inlineStr">
+      <c r="O76" s="6" t="n"/>
+      <c r="P76" s="6" t="inlineStr">
         <is>
           <t>stg2 への反映を確認してから、run-xss-data-linked.js --accept-writes で再実行する（DBダンプを取得してから）。</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="9" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>要確認（結果が未確定）</t>
         </is>
       </c>
-      <c r="D76" s="9" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>K8 受講者登録の不具合の修正後の再テスト</t>
         </is>
       </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>B-0046</t>
-        </is>
-      </c>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>管理_商品管理</t>
-        </is>
-      </c>
-      <c r="G76" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>売上(会員)(amount_user)</t>
-        </is>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>詳細(info)</t>
-        </is>
-      </c>
-      <c r="J76" s="9" t="inlineStr">
-        <is>
-          <t>hidden項目(まとめ)</t>
-        </is>
-      </c>
-      <c r="K76" s="9" t="inlineStr">
-        <is>
-          <t>/alfproduct/amount_user/info.php</t>
-        </is>
-      </c>
-      <c r="L76" s="9" t="inlineStr">
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>E-10</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>重点項目(全量一覧No別)</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>全量一覧 No.10 / 講座</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>講座確認の受講者一覧</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>受講者の氏名・メール</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>/cms_cource/confirm</t>
+        </is>
+      </c>
+      <c r="L77" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M76" s="9" t="inlineStr">
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N77" s="6" t="inlineStr">
+        <is>
+          <t>[B-13](member/regist.phpのmysql_insert_id()呼び出しでPHP8において受講者登録が失敗する不具合)によりブロックされていたが、2026-10-12時点でソースはLAST_INSERT_ID()方式に修正済みと確認。stg2への反映・再テストが必要</t>
+        </is>
+      </c>
+      <c r="O77" s="6" t="n"/>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>stg2 への反映を確認してから、run-xss-data-linked.js --accept-writes で再実行する（DBダンプを取得してから）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>要確認（結果が未確定）</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>K8 受講者登録の不具合の修正後の再テスト</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>E-12</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>重点項目(全量一覧No別)</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>全量一覧 No.12 / 売上</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>売上の会員詳細</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>受講者名</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>/alfproduct/amount_user/info.php?sid={受講者ID}</t>
+        </is>
+      </c>
+      <c r="L78" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="N76" s="9" t="inlineStr">
-        <is>
-          <t>テストハーネスの技術的制約(ページ遷移中のタイミング issue)、または[B-13]/[B-22]の修正により再テストで解消する可能性が高い</t>
-        </is>
-      </c>
-      <c r="O76" s="9" t="n"/>
-      <c r="P76" s="9" t="inlineStr">
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N78" s="6" t="inlineStr">
+        <is>
+          <t>[B-13](member/regist.phpのmysql_insert_id()呼び出しでPHP8において受講者登録が失敗する不具合)によりブロックされていたが、2026-10-12時点でソースはLAST_INSERT_ID()方式に修正済みと確認。stg2への反映・再テストが必要</t>
+        </is>
+      </c>
+      <c r="O78" s="6" t="n"/>
+      <c r="P78" s="6" t="inlineStr">
         <is>
           <t>stg2 への反映を確認してから、run-xss-data-linked.js --accept-writes で再実行する（DBダンプを取得してから）。</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="9" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>要確認（結果が未確定）</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>K8 受講者登録の不具合の修正後の再テスト</t>
         </is>
       </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>E-10</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>E-13</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>重点項目(全量一覧No別)</t>
         </is>
       </c>
-      <c r="G77" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>全量一覧 No.10 / 講座</t>
-        </is>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>講座確認の受講者一覧</t>
-        </is>
-      </c>
-      <c r="J77" s="9" t="inlineStr">
-        <is>
-          <t>受講者の氏名・メール</t>
-        </is>
-      </c>
-      <c r="K77" s="9" t="inlineStr">
-        <is>
-          <t>/cms_cource/confirm</t>
-        </is>
-      </c>
-      <c r="L77" s="9" t="inlineStr">
+      <c r="G79" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>全量一覧 No.13 / 売上</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>売上の注文詳細(確認ダイアログ)</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>受講者名(HTML・JavaScriptの2文脈)</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>/alfproduct/amount_order/info.php?oid={注文ID}</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M77" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N77" s="9" t="inlineStr">
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N79" s="6" t="inlineStr">
         <is>
           <t>[B-13](member/regist.phpのmysql_insert_id()呼び出しでPHP8において受講者登録が失敗する不具合)によりブロックされていたが、2026-10-12時点でソースはLAST_INSERT_ID()方式に修正済みと確認。stg2への反映・再テストが必要</t>
         </is>
       </c>
-      <c r="O77" s="9" t="n"/>
-      <c r="P77" s="9" t="inlineStr">
-        <is>
-          <t>stg2 への反映を確認してから、run-xss-data-linked.js --accept-writes で再実行する（DBダンプを取得してから）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="9" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>要確認（結果が未確定）</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>K8 受講者登録の不具合の修正後の再テスト</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>E-12</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>重点項目(全量一覧No別)</t>
-        </is>
-      </c>
-      <c r="G78" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>全量一覧 No.12 / 売上</t>
-        </is>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>売上の会員詳細</t>
-        </is>
-      </c>
-      <c r="J78" s="9" t="inlineStr">
-        <is>
-          <t>受講者名</t>
-        </is>
-      </c>
-      <c r="K78" s="9" t="inlineStr">
-        <is>
-          <t>/alfproduct/amount_user/info.php?sid={受講者ID}</t>
-        </is>
-      </c>
-      <c r="L78" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M78" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N78" s="9" t="inlineStr">
-        <is>
-          <t>[B-13](member/regist.phpのmysql_insert_id()呼び出しでPHP8において受講者登録が失敗する不具合)によりブロックされていたが、2026-10-12時点でソースはLAST_INSERT_ID()方式に修正済みと確認。stg2への反映・再テストが必要</t>
-        </is>
-      </c>
-      <c r="O78" s="9" t="n"/>
-      <c r="P78" s="9" t="inlineStr">
-        <is>
-          <t>stg2 への反映を確認してから、run-xss-data-linked.js --accept-writes で再実行する（DBダンプを取得してから）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="9" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr">
-        <is>
-          <t>要確認（結果が未確定）</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>K8 受講者登録の不具合の修正後の再テスト</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>E-13</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>重点項目(全量一覧No別)</t>
-        </is>
-      </c>
-      <c r="G79" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>全量一覧 No.13 / 売上</t>
-        </is>
-      </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>売上の注文詳細(確認ダイアログ)</t>
-        </is>
-      </c>
-      <c r="J79" s="9" t="inlineStr">
-        <is>
-          <t>受講者名(HTML・JavaScriptの2文脈)</t>
-        </is>
-      </c>
-      <c r="K79" s="9" t="inlineStr">
-        <is>
-          <t>/alfproduct/amount_order/info.php?oid={注文ID}</t>
-        </is>
-      </c>
-      <c r="L79" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M79" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N79" s="9" t="inlineStr">
-        <is>
-          <t>[B-13](member/regist.phpのmysql_insert_id()呼び出しでPHP8において受講者登録が失敗する不具合)によりブロックされていたが、2026-10-12時点でソースはLAST_INSERT_ID()方式に修正済みと確認。stg2への反映・再テストが必要</t>
-        </is>
-      </c>
-      <c r="O79" s="9" t="n"/>
-      <c r="P79" s="9" t="inlineStr">
+      <c r="O79" s="6" t="n"/>
+      <c r="P79" s="6" t="inlineStr">
         <is>
           <t>stg2 への反映を確認してから、run-xss-data-linked.js --accept-writes で再実行する（DBダンプを取得してから）。</t>
         </is>

--- a/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
+++ b/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
@@ -6546,7 +6546,8 @@
       <c r="O76" s="6" t="n"/>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>stg2 への反映を確認してから、run-xss-data-linked.js --accept-writes で再実行する（DBダンプを取得してから）。</t>
+          <t>【修正済み・stg2 で再テストして確認（2026-10-12）】search_orderby[] の HTTP 500 は出なくなった。売上の検索・CSV の配列の改ざん 11 パターンが、すべて HTTP 200。
+stg2 への反映を確認してから、run-xss-data-linked.js --accept-writes で再実行する（DBダンプを取得してから）。</t>
         </is>
       </c>
     </row>

--- a/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
+++ b/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
@@ -7519,74 +7519,74 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="9" t="n">
+      <c r="A90" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>要確認（結果が未確定）</t>
         </is>
       </c>
-      <c r="D90" s="9" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>K14 横断的な観点の総括確認</t>
         </is>
       </c>
-      <c r="E90" s="9" t="inlineStr">
+      <c r="E90" s="6" t="inlineStr">
         <is>
           <t>E-37</t>
         </is>
       </c>
-      <c r="F90" s="9" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <t>重点項目(全量一覧No別)</t>
         </is>
       </c>
-      <c r="G90" s="9" t="n">
+      <c r="G90" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="H90" s="9" t="inlineStr">
+      <c r="H90" s="6" t="inlineStr">
         <is>
           <t>全量一覧 No.40 / 全入力画面</t>
         </is>
       </c>
-      <c r="I90" s="9" t="inlineStr">
+      <c r="I90" s="6" t="inlineStr">
         <is>
           <t>入力フィルタ(xss_clean)の除去</t>
         </is>
       </c>
-      <c r="J90" s="9" t="inlineStr">
+      <c r="J90" s="6" t="inlineStr">
         <is>
           <t>保存される値</t>
         </is>
       </c>
-      <c r="K90" s="9" t="inlineStr">
+      <c r="K90" s="6" t="inlineStr">
         <is>
           <t>/(全入力画面)</t>
         </is>
       </c>
-      <c r="L90" s="9" t="inlineStr">
+      <c r="L90" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M90" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N90" s="9" t="inlineStr">
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N90" s="6" t="inlineStr">
         <is>
           <t>横断的な観点(全入力画面の入力値往復・PC/SP差分)の総括確認はまだ。個別画面の確認は既存のS1〜S12テストで広くカバー済み</t>
         </is>
       </c>
-      <c r="O90" s="9" t="n"/>
-      <c r="P90" s="9" t="inlineStr">
+      <c r="O90" s="6" t="n"/>
+      <c r="P90" s="6" t="inlineStr">
         <is>
           <t>個別画面のテスト結果をもとに、観点ごとに総括して判定する。</t>
         </is>

--- a/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
+++ b/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
@@ -5270,7 +5270,11 @@
           <t>ログ・本番DB比較・インフラ設定比較等、ブラウザでは確認できない運用上の確認事項。人による確認が必要</t>
         </is>
       </c>
-      <c r="O59" s="9" t="n"/>
+      <c r="O59" s="9" t="inlineStr">
+        <is>
+          <t>[途中経過。結果は「要確認」のまま] stg2 で確認した表示先: 管理画面（CMS）、商品管理（一覧・登録画面・売上の会員詳細・注文詳細・レポート）、受講者サイト（PC・スマートフォン）、WordPress（トップ・お知らせ一覧・記事）、受講票 PDF・受講履歴の印刷画面・領収書 PDF（宛名の攻撃文字列は、文字として印字）。未確認: CSV（Excel で開いたときの式の実行）、メール（自動返信・問い合わせ）、本番での表示。手順: 確認手順_E-35_E-36_E-39_E-44_2026-10-12.md の 3。</t>
+        </is>
+      </c>
       <c r="P59" s="9" t="inlineStr">
         <is>
           <t>ログ・本番DB・インフラの設定などを人が確認する（E-39 は反映時のソースの差分確認など）。</t>
@@ -5571,7 +5575,11 @@
           <t>ログ・本番DB比較・インフラ設定比較等、ブラウザでは確認できない運用上の確認事項。人による確認が必要</t>
         </is>
       </c>
-      <c r="O63" s="9" t="n"/>
+      <c r="O63" s="9" t="inlineStr">
+        <is>
+          <t>[途中経過。結果は「要確認」のまま] 入口の表 G-09（WordPress への自動投稿）・G-11（メルマガ）・G-12（決済事業者からの戻り）は OK。stg2 の PDF（受講票・領収書）・印刷画面は確認済み。未確認: CSV の式の実行、メール、本番。手順: 確認手順_E-35_E-36_E-39_E-44_2026-10-12.md の 3。</t>
+        </is>
+      </c>
       <c r="P63" s="9" t="inlineStr">
         <is>
           <t>ログ・本番DB・インフラの設定などを人が確認する（E-39 は反映時のソースの差分確認など）。</t>

--- a/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
+++ b/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
@@ -5348,7 +5348,11 @@
           <t>ログ・本番DB比較・インフラ設定比較等、ブラウザでは確認できない運用上の確認事項。人による確認が必要</t>
         </is>
       </c>
-      <c r="O60" s="9" t="n"/>
+      <c r="O60" s="9" t="inlineStr">
+        <is>
+          <t>[途中経過。結果は「要確認」のまま（本番での実施が残っている）] stg2 でリハーサルを実施した。①tbl_product（15商品・44件）: 手順3・4 を実行し、旧値 0 件・新値 44 件。手順2のバックアップ（CREATE TABLE ... AS SELECT）は、#1118 Row size too large で失敗したため、SQL を CREATE TABLE ... LIKE ＋ INSERT に修正した（tbl_product 全体のダンプを、代わりのバックアップに取得）。画面: 商品管理の商品詳細で、24577・19674 は HTML で1回だけエスケープ（&amp;amp; が二重にならない）、13 のダウンロード名に &amp;nbsp; なし。商品 24577 を、編集画面から変更せずに再保存（確認→登録）しても、値は戻らなかった（二重エスケープなし）。②追加で発見: tbl_product_live_training.memo2（商品14206の「講義タイトル、講師名」）に、同じ旧値（姜&amp;#22989;）が残っていた。No.39 の SQL は tbl_product だけが対象だったため、追加手順（バックアップ・更新・確認）を SQL に追加し、stg2 で実行（1件）。管理画面の商品詳細（product_live/info.php?mid=14206）で、姜姍（中国律師）の表示を確認した。データベース内検索（旧値の正規表現）で、tbl_product_add・tbl_product_ethic_training・tbl_product_ethic_passport・tbl_product_passing・tbl_product_passport は 0 件。tbl_product・tbl_product_elearning・tbl_product_live_training の残りの一致は、テストで登録した商品（26315・26317・26318・26320・26321・26323・26324）の入力値で、対象外。未実施: 本番での実行（本番も、tbl_product 以外の表を、データベース内検索で先に確認する）。</t>
+        </is>
+      </c>
       <c r="P60" s="9" t="inlineStr">
         <is>
           <t>ログ・本番DB・インフラの設定などを人が確認する（E-39 は反映時のソースの差分確認など）。</t>

--- a/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
+++ b/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
@@ -5272,7 +5272,7 @@
       </c>
       <c r="O59" s="9" t="inlineStr">
         <is>
-          <t>[途中経過。結果は「要確認」のまま] stg2 で確認した表示先: 管理画面（CMS）、商品管理（一覧・登録画面・売上の会員詳細・注文詳細・レポート）、受講者サイト（PC・スマートフォン）、WordPress（トップ・お知らせ一覧・記事）、受講票 PDF・受講履歴の印刷画面・領収書 PDF（宛名の攻撃文字列は、文字として印字）。未確認: CSV（Excel で開いたときの式の実行）、メール（自動返信・問い合わせ）、本番での表示。手順: 確認手順_E-35_E-36_E-39_E-44_2026-10-12.md の 3。</t>
+          <t>[途中経過。結果は「要確認」のまま] stg2 で確認した表示先: 管理画面（CMS）、商品管理（一覧・登録画面・売上の会員詳細・注文詳細・レポート）、受講者サイト（PC・スマートフォン）、WordPress（トップ・お知らせ一覧・記事）、受講票 PDF・受講履歴の印刷画面・領収書 PDF（宛名の攻撃文字列は、文字として印字）、CSV。未確認: メール（自動返信・問い合わせ）、本番での表示。 CSV（stg2）: 数式の実行（CSV インジェクション）の対策を確認した。①関数 csv_formula_safe() を、手元の PHP で 24 パターン確認（=・+・-・@・タブ・改行で始まる値は、先頭に ' が付く。-5・+3 などの数値は、そのまま）。②stg2 の実機: 受講者別（約 5 万行）・商品別・パスポート・会場研修（もともと数式の形の 6 件に ' が付いていた）・倫理研修の CSV を取得し、式として動く値は 0 件。③受講者 36366（登録番号 500999）の氏名を、SQL で =1+1 に変えて、受講者別 CSV と売上（注文）CSV（登録番号 500999 で検索。3003 行）を取得し、氏名の欄が、すべて '=1+1 になることを確認した（確認後に、氏名を元に戻す）。注意: 売上（注文）の CSV は、検索条件なしで出すと、HTTP 500（メモリ不足 805306368 バイト。DbConnect.php:49）になる（全注文を一度に読み込むため。今回の変更が原因ではなくデータ量によるものと見られる。本番も同様の可能性がある）。 手順: 確認手順_E-35_E-36_E-39_E-44_2026-10-12.md の 3。</t>
         </is>
       </c>
       <c r="P59" s="9" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="O63" s="9" t="inlineStr">
         <is>
-          <t>[途中経過。結果は「要確認」のまま] 入口の表 G-09（WordPress への自動投稿）・G-11（メルマガ）・G-12（決済事業者からの戻り）は OK。stg2 の PDF（受講票・領収書）・印刷画面は確認済み。未確認: CSV の式の実行、メール、本番。手順: 確認手順_E-35_E-36_E-39_E-44_2026-10-12.md の 3。</t>
+          <t>[途中経過。結果は「要確認」のまま] 入口の表 G-09（WordPress への自動投稿）・G-11（メルマガ）・G-12（決済事業者からの戻り）は OK。stg2 の PDF（受講票・領収書）・印刷画面・CSV は確認済み。未確認: メール、本番。 CSV（stg2）: 数式の実行（CSV インジェクション）の対策を確認した。①関数 csv_formula_safe() を、手元の PHP で 24 パターン確認（=・+・-・@・タブ・改行で始まる値は、先頭に ' が付く。-5・+3 などの数値は、そのまま）。②stg2 の実機: 受講者別（約 5 万行）・商品別・パスポート・会場研修（もともと数式の形の 6 件に ' が付いていた）・倫理研修の CSV を取得し、式として動く値は 0 件。③受講者 36366（登録番号 500999）の氏名を、SQL で =1+1 に変えて、受講者別 CSV と売上（注文）CSV（登録番号 500999 で検索。3003 行）を取得し、氏名の欄が、すべて '=1+1 になることを確認した（確認後に、氏名を元に戻す）。注意: 売上（注文）の CSV は、検索条件なしで出すと、HTTP 500（メモリ不足 805306368 バイト。DbConnect.php:49）になる（全注文を一度に読み込むため。今回の変更が原因ではなくデータ量によるものと見られる。本番も同様の可能性がある）。 手順: 確認手順_E-35_E-36_E-39_E-44_2026-10-12.md の 3。</t>
         </is>
       </c>
       <c r="P63" s="9" t="inlineStr">

--- a/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
+++ b/secure_report/XSS対応_脆弱性テスト計画_未テスト項目一覧_2026-10-12.xlsx
@@ -5204,156 +5204,156 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="9" t="n">
+      <c r="A59" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>要確認（結果が未確定）</t>
         </is>
       </c>
-      <c r="D59" s="9" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>K5 ブラウザでは確認できない運用上の項目</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>E-35</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>重点項目(全量一覧No別)</t>
         </is>
       </c>
-      <c r="G59" s="9" t="n">
+      <c r="G59" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="H59" s="9" t="inlineStr">
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>全量一覧 No.38 / 全画面</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
+      <c r="I59" s="6" t="inlineStr">
         <is>
           <t>表示方式の統一</t>
         </is>
       </c>
-      <c r="J59" s="9" t="inlineStr">
+      <c r="J59" s="6" t="inlineStr">
         <is>
           <t>同じデータの見え方</t>
         </is>
       </c>
-      <c r="K59" s="9" t="inlineStr">
+      <c r="K59" s="6" t="inlineStr">
         <is>
           <t>(管理画面・商品管理・受講者サイト・WordPress)</t>
         </is>
       </c>
-      <c r="L59" s="9" t="inlineStr">
+      <c r="L59" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M59" s="9" t="inlineStr">
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N59" s="6" t="inlineStr">
+        <is>
+          <t>ログ・本番DB比較・インフラ設定比較等、ブラウザでは確認できない運用上の確認事項。人による確認が必要</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="inlineStr">
+        <is>
+          <t>[完了] stg2 で確認できる範囲は、確認済み: 管理画面（CMS）、商品管理（一覧・登録画面・売上の会員詳細・注文詳細・レポート）、受講者サイト（PC・スマートフォン）、WordPress（トップ・お知らせ一覧・記事）、受講票 PDF・受講履歴の印刷画面・領収書 PDF（宛名の攻撃文字列は、文字として印字）、CSV（数式の対策。氏名 =1+1 が '=1+1 で出力）。 メール: ①問い合わせフォーム（inquiry/send.php）の mail() は、最初のコミットからコメントアウトされていて、メールは送られない（DB に保存されるだけ）。②購入・入金確認のメール（payment_card・payment_bank・payment_free・payment_passport_user・amount_order/info.php・bank_upload）は、本文がテキスト形式で、氏名・商品名が本文にだけ入る（件名は固定）。ソースで確認した。③管理画面の問い合わせ返信（inquiry/regist.php）の宛先が、受講者の入力（検査は、空でないことだけ）をそのまま使っていたため、メールヘッダーインジェクションのおそれがあり、修正した（問い合わせフォームのメールアドレスに、改行・NUL を含む値を拒否、返信の宛先から除去）。stg2 で、改行・NUL 入りの値がエラーになり、通常の値は通ることを確認。配列送信で 500 になる点も、request_str() に変更して修正した。④stg2 で、実際の送信を試した（受講者 36366 の氏名を攻撃文字列、メールアドレスをテスト用アドレスにして、注文 2135278 の明細 2146749 を入金済に変更）が、届かなかった。stg2 のサーバーに、sendmail がなく（which sendmail が見つからない）、maillog も空（10/6〜10/12）で、メールを送れない環境のため、実際のメールの内容は、stg2 では確認できない。 本番: 反映後に、本番で、入金確認メールを実際に送り、本文・件名・差出人を確認する（運用項目）。</t>
+        </is>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>ログ・本番DB・インフラの設定などを人が確認する（E-39 は反映時のソースの差分確認など）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>要確認（結果が未確定）</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>K5 ブラウザでは確認できない運用上の項目</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>E-36</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>重点項目(全量一覧No別)</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>全量一覧 No.39 / 商品管理</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>保存済みデータの修正</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>44件のUPDATE</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>(データベース)</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="N59" s="9" t="inlineStr">
+      <c r="M60" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N60" s="6" t="inlineStr">
         <is>
           <t>ログ・本番DB比較・インフラ設定比較等、ブラウザでは確認できない運用上の確認事項。人による確認が必要</t>
         </is>
       </c>
-      <c r="O59" s="9" t="inlineStr">
-        <is>
-          <t>[途中経過。結果は「要確認」のまま] stg2 で確認した表示先: 管理画面（CMS）、商品管理（一覧・登録画面・売上の会員詳細・注文詳細・レポート）、受講者サイト（PC・スマートフォン）、WordPress（トップ・お知らせ一覧・記事）、受講票 PDF・受講履歴の印刷画面・領収書 PDF（宛名の攻撃文字列は、文字として印字）、CSV。未確認: メール（自動返信・問い合わせ）、本番での表示。 CSV（stg2）: 数式の実行（CSV インジェクション）の対策を確認した。①関数 csv_formula_safe() を、手元の PHP で 24 パターン確認（=・+・-・@・タブ・改行で始まる値は、先頭に ' が付く。-5・+3 などの数値は、そのまま）。②stg2 の実機: 受講者別（約 5 万行）・商品別・パスポート・会場研修（もともと数式の形の 6 件に ' が付いていた）・倫理研修の CSV を取得し、式として動く値は 0 件。③受講者 36366（登録番号 500999）の氏名を、SQL で =1+1 に変えて、受講者別 CSV と売上（注文）CSV（登録番号 500999 で検索。3003 行）を取得し、氏名の欄が、すべて '=1+1 になることを確認した（確認後に、氏名を元に戻す）。注意: 売上（注文）の CSV は、検索条件なしで出すと、HTTP 500（メモリ不足 805306368 バイト。DbConnect.php:49）になる（全注文を一度に読み込むため。今回の変更が原因ではなくデータ量によるものと見られる。本番も同様の可能性がある）。 手順: 確認手順_E-35_E-36_E-39_E-44_2026-10-12.md の 3。</t>
-        </is>
-      </c>
-      <c r="P59" s="9" t="inlineStr">
-        <is>
-          <t>ログ・本番DB・インフラの設定などを人が確認する（E-39 は反映時のソースの差分確認など）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>要確認（結果が未確定）</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>K5 ブラウザでは確認できない運用上の項目</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>E-36</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="inlineStr">
-        <is>
-          <t>重点項目(全量一覧No別)</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>全量一覧 No.39 / 商品管理</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>保存済みデータの修正</t>
-        </is>
-      </c>
-      <c r="J60" s="9" t="inlineStr">
-        <is>
-          <t>44件のUPDATE</t>
-        </is>
-      </c>
-      <c r="K60" s="9" t="inlineStr">
-        <is>
-          <t>(データベース)</t>
-        </is>
-      </c>
-      <c r="L60" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M60" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N60" s="9" t="inlineStr">
-        <is>
-          <t>ログ・本番DB比較・インフラ設定比較等、ブラウザでは確認できない運用上の確認事項。人による確認が必要</t>
-        </is>
-      </c>
-      <c r="O60" s="9" t="inlineStr">
+      <c r="O60" s="6" t="inlineStr">
         <is>
           <t>[途中経過。結果は「要確認」のまま（本番での実施が残っている）] stg2 でリハーサルを実施した。①tbl_product（15商品・44件）: 手順3・4 を実行し、旧値 0 件・新値 44 件。手順2のバックアップ（CREATE TABLE ... AS SELECT）は、#1118 Row size too large で失敗したため、SQL を CREATE TABLE ... LIKE ＋ INSERT に修正した（tbl_product 全体のダンプを、代わりのバックアップに取得）。画面: 商品管理の商品詳細で、24577・19674 は HTML で1回だけエスケープ（&amp;amp; が二重にならない）、13 のダウンロード名に &amp;nbsp; なし。商品 24577 を、編集画面から変更せずに再保存（確認→登録）しても、値は戻らなかった（二重エスケープなし）。②追加で発見: tbl_product_live_training.memo2（商品14206の「講義タイトル、講師名」）に、同じ旧値（姜&amp;#22989;）が残っていた。No.39 の SQL は tbl_product だけが対象だったため、追加手順（バックアップ・更新・確認）を SQL に追加し、stg2 で実行（1件）。管理画面の商品詳細（product_live/info.php?mid=14206）で、姜姍（中国律師）の表示を確認した。データベース内検索（旧値の正規表現）で、tbl_product_add・tbl_product_ethic_training・tbl_product_ethic_passport・tbl_product_passing・tbl_product_passport は 0 件。tbl_product・tbl_product_elearning・tbl_product_live_training の残りの一致は、テストで登録した商品（26315・26317・26318・26320・26321・26323・26324）の入力値で、対象外。未実施: 本番での実行（本番も、tbl_product 以外の表を、データベース内検索で先に確認する）。</t>
         </is>
       </c>
-      <c r="P60" s="9" t="inlineStr">
+      <c r="P60" s="6" t="inlineStr">
         <is>
           <t>ログ・本番DB・インフラの設定などを人が確認する（E-39 は反映時のソースの差分確認など）。</t>
         </is>
@@ -5439,152 +5439,152 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="n">
+      <c r="A62" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>要確認（結果が未確定）</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>K5 ブラウザでは確認できない運用上の項目</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="E62" s="6" t="inlineStr">
         <is>
           <t>E-39</t>
         </is>
       </c>
-      <c r="F62" s="9" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <t>重点項目(全量一覧No別)</t>
         </is>
       </c>
-      <c r="G62" s="9" t="n">
+      <c r="G62" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="H62" s="9" t="inlineStr">
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>全量一覧 No.42 / 全体</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>検証環境と本番の差</t>
         </is>
       </c>
-      <c r="J62" s="9" t="inlineStr">
+      <c r="J62" s="6" t="inlineStr">
         <is>
           <t>ファイル差分</t>
         </is>
       </c>
-      <c r="K62" s="9" t="inlineStr">
+      <c r="K62" s="6" t="inlineStr">
         <is>
           <t>(デプロイ差分)</t>
         </is>
       </c>
-      <c r="L62" s="9" t="inlineStr">
+      <c r="L62" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="M62" s="9" t="inlineStr">
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>ログ・本番DB比較・インフラ設定比較等、ブラウザでは確認できない運用上の確認事項。人による確認が必要</t>
+        </is>
+      </c>
+      <c r="O62" s="6" t="n"/>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>ログ・本番DB・インフラの設定などを人が確認する（E-39 は反映時のソースの差分確認など）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>対応済み</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>要確認（結果が未確定）</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>K5 ブラウザでは確認できない運用上の項目</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>E-44</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>重点項目(全量一覧No別)</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>全量一覧 No.47 / 全体</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>複数システムへの受け渡し</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>同じデータの全表示先</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>(管理・受講者サイト・WordPress・CSV・メール・PDF)</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="N62" s="9" t="inlineStr">
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N63" s="6" t="inlineStr">
         <is>
           <t>ログ・本番DB比較・インフラ設定比較等、ブラウザでは確認できない運用上の確認事項。人による確認が必要</t>
         </is>
       </c>
-      <c r="O62" s="9" t="n"/>
-      <c r="P62" s="9" t="inlineStr">
-        <is>
-          <t>ログ・本番DB・インフラの設定などを人が確認する（E-39 は反映時のソースの差分確認など）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>未対応</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>要確認（結果が未確定）</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>K5 ブラウザでは確認できない運用上の項目</t>
-        </is>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>E-44</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="inlineStr">
-        <is>
-          <t>重点項目(全量一覧No別)</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="n">
-        <v>48</v>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>全量一覧 No.47 / 全体</t>
-        </is>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>複数システムへの受け渡し</t>
-        </is>
-      </c>
-      <c r="J63" s="9" t="inlineStr">
-        <is>
-          <t>同じデータの全表示先</t>
-        </is>
-      </c>
-      <c r="K63" s="9" t="inlineStr">
-        <is>
-          <t>(管理・受講者サイト・WordPress・CSV・メール・PDF)</t>
-        </is>
-      </c>
-      <c r="L63" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="M63" s="9" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="N63" s="9" t="inlineStr">
-        <is>
-          <t>ログ・本番DB比較・インフラ設定比較等、ブラウザでは確認できない運用上の確認事項。人による確認が必要</t>
-        </is>
-      </c>
-      <c r="O63" s="9" t="inlineStr">
-        <is>
-          <t>[途中経過。結果は「要確認」のまま] 入口の表 G-09（WordPress への自動投稿）・G-11（メルマガ）・G-12（決済事業者からの戻り）は OK。stg2 の PDF（受講票・領収書）・印刷画面・CSV は確認済み。未確認: メール、本番。 CSV（stg2）: 数式の実行（CSV インジェクション）の対策を確認した。①関数 csv_formula_safe() を、手元の PHP で 24 パターン確認（=・+・-・@・タブ・改行で始まる値は、先頭に ' が付く。-5・+3 などの数値は、そのまま）。②stg2 の実機: 受講者別（約 5 万行）・商品別・パスポート・会場研修（もともと数式の形の 6 件に ' が付いていた）・倫理研修の CSV を取得し、式として動く値は 0 件。③受講者 36366（登録番号 500999）の氏名を、SQL で =1+1 に変えて、受講者別 CSV と売上（注文）CSV（登録番号 500999 で検索。3003 行）を取得し、氏名の欄が、すべて '=1+1 になることを確認した（確認後に、氏名を元に戻す）。注意: 売上（注文）の CSV は、検索条件なしで出すと、HTTP 500（メモリ不足 805306368 バイト。DbConnect.php:49）になる（全注文を一度に読み込むため。今回の変更が原因ではなくデータ量によるものと見られる。本番も同様の可能性がある）。 手順: 確認手順_E-35_E-36_E-39_E-44_2026-10-12.md の 3。</t>
-        </is>
-      </c>
-      <c r="P63" s="9" t="inlineStr">
+      <c r="O63" s="6" t="inlineStr">
+        <is>
+          <t>[完了] 入口の表 G-09（WordPress への自動投稿）・G-11（メルマガ）・G-12（決済事業者からの戻り）は OK。stg2 の PDF（受講票・領収書）・印刷画面・CSV は確認済み。 メール: ①問い合わせフォーム（inquiry/send.php）の mail() は、最初のコミットからコメントアウトされていて、メールは送られない（DB に保存されるだけ）。②購入・入金確認のメール（payment_card・payment_bank・payment_free・payment_passport_user・amount_order/info.php・bank_upload）は、本文がテキスト形式で、氏名・商品名が本文にだけ入る（件名は固定）。ソースで確認した。③管理画面の問い合わせ返信（inquiry/regist.php）の宛先が、受講者の入力（検査は、空でないことだけ）をそのまま使っていたため、メールヘッダーインジェクションのおそれがあり、修正した（問い合わせフォームのメールアドレスに、改行・NUL を含む値を拒否、返信の宛先から除去）。stg2 で、改行・NUL 入りの値がエラーになり、通常の値は通ることを確認。配列送信で 500 になる点も、request_str() に変更して修正した。④stg2 で、実際の送信を試した（受講者 36366 の氏名を攻撃文字列、メールアドレスをテスト用アドレスにして、注文 2135278 の明細 2146749 を入金済に変更）が、届かなかった。stg2 のサーバーに、sendmail がなく（which sendmail が見つからない）、maillog も空（10/6〜10/12）で、メールを送れない環境のため、実際のメールの内容は、stg2 では確認できない。 本番: 反映後に、本番で、入金確認メールを実際に送り、本文・件名・差出人を確認する（運用項目）。</t>
+        </is>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
         <is>
           <t>ログ・本番DB・インフラの設定などを人が確認する（E-39 は反映時のソースの差分確認など）。</t>
         </is>
